--- a/files/九龙-何文田-耀爵台.xlsx
+++ b/files/九龙-何文田-耀爵台.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-06-18</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-08-13</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1459,7 +1459,7 @@
           <t>- | 1988呎 (4+房)
 $6550万
 $32,948/呎
-(已售)</t>
+(18年-08月)</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
           <t>- | 982呎 (3房)
 $2050万
 $20,876/呎
-(已售)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
           <t>- | 982呎 (3房)
 $2030万
 $20,672/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
           <t>- | 982呎 (3房)
 $2286万
 $23,279/呎
-(已售)</t>
+(15年-06月)</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
           <t>- | 982呎 (3房)
 $1928万
 $19,633/呎
-(已售)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
           <t>- | 982呎 (3房)
 $1848万
 $18,819/呎
-(已售)</t>
+(19年-08月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-耀爵台.xlsx
+++ b/files/九龙-何文田-耀爵台.xlsx
@@ -198,61 +198,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -635,7 +635,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-何文田-耀爵台.xlsx
+++ b/files/九龙-何文田-耀爵台.xlsx
@@ -198,61 +198,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -635,7 +635,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
